--- a/Case_Studies/Java & Angular-Batch 1-Project evaluation sheet.xlsx
+++ b/Case_Studies/Java & Angular-Batch 1-Project evaluation sheet.xlsx
@@ -1064,7 +1064,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
